--- a/data/trans_orig/P57B3_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P57B3_2023-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según se ha sentido solo/a en 2023</t>
+          <t>Población según se ha sentido solo/a en 2023 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8137</t>
+          <t>7758</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23532</t>
+          <t>22905</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5926</t>
+          <t>6064</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16139</t>
+          <t>15654</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16261</t>
+          <t>16243</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33183</t>
+          <t>33401</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,51%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21586</t>
+          <t>22315</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>46262</t>
+          <t>46159</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20138</t>
+          <t>19644</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>37595</t>
+          <t>36976</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>47380</t>
+          <t>46936</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>77422</t>
+          <t>75943</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>7,98%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>118116</t>
+          <t>117662</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>158334</t>
+          <t>158282</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>113682</t>
+          <t>114365</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>147704</t>
+          <t>144958</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>32,4%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>241767</t>
+          <t>241377</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>295550</t>
+          <t>297202</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>31,23%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>297345</t>
+          <t>299572</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>341976</t>
+          <t>342792</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>58,98%</t>
+          <t>59,42%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>67,83%</t>
+          <t>67,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>262476</t>
+          <t>264034</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>297199</t>
+          <t>295953</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>58,66%</t>
+          <t>59,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>66,42%</t>
+          <t>66,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>573032</t>
+          <t>570884</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>629099</t>
+          <t>628635</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>60,21%</t>
+          <t>59,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>66,11%</t>
+          <t>66,06%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7266</t>
+          <t>7799</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>19664</t>
+          <t>21638</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7174</t>
+          <t>6734</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>18085</t>
+          <t>17954</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>16895</t>
+          <t>16371</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>33719</t>
+          <t>33269</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,99%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18409</t>
+          <t>18207</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>37353</t>
+          <t>36011</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19018</t>
+          <t>18223</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>34316</t>
+          <t>34306</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>40155</t>
+          <t>40713</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>64512</t>
+          <t>63885</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,67%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>142641</t>
+          <t>141132</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>184092</t>
+          <t>182284</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>40,71%</t>
+          <t>40,31%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>100713</t>
+          <t>100506</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>131405</t>
+          <t>130274</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>249965</t>
+          <t>252440</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>301579</t>
+          <t>300331</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>36,05%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>230617</t>
+          <t>231694</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>273631</t>
+          <t>275433</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>51,0%</t>
+          <t>51,24%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>60,51%</t>
+          <t>60,91%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>211641</t>
+          <t>212070</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>244816</t>
+          <t>243680</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>55,56%</t>
+          <t>55,67%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>64,27%</t>
+          <t>63,97%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>453223</t>
+          <t>453352</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>509920</t>
+          <t>506415</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>54,4%</t>
+          <t>54,42%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>61,21%</t>
+          <t>60,79%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>25289</t>
+          <t>23960</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>521961</t>
+          <t>504349</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,11%</t>
+          <t>75,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3723</t>
+          <t>3687</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>11306</t>
+          <t>11234</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>31313</t>
+          <t>32142</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>595727</t>
+          <t>571503</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,33%</t>
+          <t>68,43%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11894</t>
+          <t>11018</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>55512</t>
+          <t>55318</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>13324</t>
+          <t>13485</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>26073</t>
+          <t>25980</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>21448</t>
+          <t>22623</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>79072</t>
+          <t>77393</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,27%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>44160</t>
+          <t>49747</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>196624</t>
+          <t>197786</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>44302</t>
+          <t>44796</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>64045</t>
+          <t>63678</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>38,37%</t>
+          <t>38,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>73232</t>
+          <t>77012</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>250467</t>
+          <t>247059</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>29,58%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>88968</t>
+          <t>98187</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>409286</t>
+          <t>413198</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>61,25%</t>
+          <t>61,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>77220</t>
+          <t>76747</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>97585</t>
+          <t>96973</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>46,26%</t>
+          <t>45,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>58,47%</t>
+          <t>58,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>143429</t>
+          <t>162813</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>493231</t>
+          <t>496533</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>59,06%</t>
+          <t>59,45%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>30195</t>
+          <t>30212</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>52391</t>
+          <t>52562</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10511</t>
+          <t>12140</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>35511</t>
+          <t>35273</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>44376</t>
+          <t>42679</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>80845</t>
+          <t>79207</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,94%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>75041</t>
+          <t>75707</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>111261</t>
+          <t>110873</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>25102</t>
+          <t>25744</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>68957</t>
+          <t>70847</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,47 +2600,47 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
+          <t>7,24%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>141836</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>96976</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>169177</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
           <t>7,05%</t>
         </is>
       </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>141836</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>97152</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>169445</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>7,05%</t>
-        </is>
-      </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,41%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>314875</t>
+          <t>315544</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>385740</t>
+          <t>385291</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>37,26%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>127673</t>
+          <t>144176</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>330225</t>
+          <t>329296</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>33,67%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>416672</t>
+          <t>401845</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>680461</t>
+          <t>684226</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>34,01%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>518958</t>
+          <t>514921</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>588403</t>
+          <t>587462</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>50,19%</t>
+          <t>49,8%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>56,91%</t>
+          <t>56,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>555736</t>
+          <t>554960</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>805950</t>
+          <t>783818</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>56,82%</t>
+          <t>56,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>82,4%</t>
+          <t>80,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1097957</t>
+          <t>1100277</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1456752</t>
+          <t>1476834</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>54,57%</t>
+          <t>54,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>72,4%</t>
+          <t>73,4%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>25053</t>
+          <t>24596</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>47310</t>
+          <t>45228</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>36072</t>
+          <t>35729</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>61643</t>
+          <t>60836</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>65190</t>
+          <t>66351</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>99837</t>
+          <t>101333</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,71%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>38006</t>
+          <t>38741</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>62630</t>
+          <t>64021</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>68261</t>
+          <t>65888</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>109636</t>
+          <t>108383</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>113672</t>
+          <t>113947</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>162961</t>
+          <t>162574</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,36%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>147894</t>
+          <t>148484</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>194452</t>
+          <t>196585</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>40,93%</t>
+          <t>41,38%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>199083</t>
+          <t>201440</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>304476</t>
+          <t>303760</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>36,17%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>354381</t>
+          <t>361325</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>481820</t>
+          <t>478044</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>36,36%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>196371</t>
+          <t>197674</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>243136</t>
+          <t>243924</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>41,34%</t>
+          <t>41,61%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>51,18%</t>
+          <t>51,35%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>380948</t>
+          <t>383101</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>532134</t>
+          <t>531864</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>45,36%</t>
+          <t>45,62%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>63,36%</t>
+          <t>63,33%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>598160</t>
+          <t>598418</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>784754</t>
+          <t>783349</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>45,49%</t>
+          <t>45,51%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>59,68%</t>
+          <t>59,58%</t>
         </is>
       </c>
     </row>
@@ -3575,12 +3575,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>493</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>6931</t>
+          <t>7139</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>27577</t>
+          <t>27924</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>48159</t>
+          <t>49535</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>29630</t>
+          <t>30131</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>51143</t>
+          <t>53246</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,33%</t>
         </is>
       </c>
     </row>
@@ -3688,12 +3688,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2486</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>20171</t>
+          <t>20483</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>67842</t>
+          <t>66958</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>98026</t>
+          <t>94967</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>74149</t>
+          <t>73136</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>106110</t>
+          <t>105937</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,12 +3773,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,6%</t>
         </is>
       </c>
     </row>
@@ -3801,12 +3801,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>51652</t>
+          <t>52067</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>100508</t>
+          <t>102816</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>42,75%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>265439</t>
+          <t>267377</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>317556</t>
+          <t>319517</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>35,22%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>41,83%</t>
+          <t>42,09%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>332296</t>
+          <t>332048</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>398374</t>
+          <t>404208</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>33,22%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>39,85%</t>
+          <t>40,44%</t>
         </is>
       </c>
     </row>
@@ -3914,12 +3914,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>131224</t>
+          <t>128858</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>180159</t>
+          <t>179772</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3929,12 +3929,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>54,56%</t>
+          <t>53,58%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>74,91%</t>
+          <t>74,75%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3949,12 +3949,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>324647</t>
+          <t>325846</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>376472</t>
+          <t>377205</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3964,12 +3964,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>42,77%</t>
+          <t>42,92%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>49,59%</t>
+          <t>49,69%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>471599</t>
+          <t>468444</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>545372</t>
+          <t>544309</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>47,18%</t>
+          <t>46,86%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>54,56%</t>
+          <t>54,45%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>124472</t>
+          <t>123777</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>1042686</t>
+          <t>1182880</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>35,06%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>111920</t>
+          <t>111684</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>159587</t>
+          <t>158726</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>256370</t>
+          <t>258132</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>1528605</t>
+          <t>1314002</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>18,92%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>186809</t>
+          <t>186223</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>272562</t>
+          <t>276516</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>241581</t>
+          <t>235939</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>328245</t>
+          <t>326710</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>455716</t>
+          <t>461734</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>584098</t>
+          <t>584809</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,42%</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>787418</t>
+          <t>755489</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>1111430</t>
+          <t>1116313</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>913453</t>
+          <t>885868</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>1202329</t>
+          <t>1202126</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1835729</t>
+          <t>1859917</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>2281259</t>
+          <t>2270272</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>32,68%</t>
         </is>
       </c>
     </row>
@@ -4483,12 +4483,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1347050</t>
+          <t>1267274</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1918162</t>
+          <t>1917814</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>39,92%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>56,85%</t>
+          <t>56,84%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1910657</t>
+          <t>1914922</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>2302758</t>
+          <t>2347612</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>53,49%</t>
+          <t>53,6%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>64,46%</t>
+          <t>65,72%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>3332240</t>
+          <t>3375226</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>4044733</t>
+          <t>4061754</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>47,97%</t>
+          <t>48,59%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>58,23%</t>
+          <t>58,47%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P57B3_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P57B3_2023-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>13593</t>
+          <t>14382</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7758</t>
+          <t>8268</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22905</t>
+          <t>23707</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>10120</t>
+          <t>12021</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6064</t>
+          <t>7164</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15654</t>
+          <t>18675</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>23713</t>
+          <t>26404</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16243</t>
+          <t>18520</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33401</t>
+          <t>36566</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,52%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>32084</t>
+          <t>37595</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22315</t>
+          <t>26004</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>46159</t>
+          <t>52333</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>27488</t>
+          <t>32974</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19644</t>
+          <t>22947</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>36976</t>
+          <t>43477</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>59572</t>
+          <t>70570</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>46936</t>
+          <t>52934</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>75943</t>
+          <t>88687</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,55%</t>
         </is>
       </c>
     </row>
@@ -951,22 +951,22 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>137685</t>
+          <t>148850</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>117662</t>
+          <t>128266</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>158282</t>
+          <t>170926</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>129659</t>
+          <t>140313</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>114365</t>
+          <t>124095</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>144958</t>
+          <t>158817</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>267344</t>
+          <t>289163</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>241377</t>
+          <t>264188</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>297202</t>
+          <t>316875</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>30,53%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>320825</t>
+          <t>348636</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>299572</t>
+          <t>325634</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>342792</t>
+          <t>373464</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>63,63%</t>
+          <t>63,45%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>59,42%</t>
+          <t>59,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>67,99%</t>
+          <t>67,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>280199</t>
+          <t>303102</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>264034</t>
+          <t>283528</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>295953</t>
+          <t>320755</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>62,62%</t>
+          <t>62,06%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>59,01%</t>
+          <t>58,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>66,14%</t>
+          <t>65,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>601024</t>
+          <t>651739</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>570884</t>
+          <t>624060</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>628635</t>
+          <t>682474</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>63,16%</t>
+          <t>62,8%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>59,99%</t>
+          <t>60,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>66,06%</t>
+          <t>65,76%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>504187</t>
+          <t>549464</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>504187</t>
+          <t>549464</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>504187</t>
+          <t>549464</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>951654</t>
+          <t>1037875</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>951654</t>
+          <t>1037875</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>951654</t>
+          <t>1037875</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12401</t>
+          <t>13410</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7799</t>
+          <t>7595</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>21638</t>
+          <t>21464</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11434</t>
+          <t>13992</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6734</t>
+          <t>9302</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17954</t>
+          <t>21958</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>23835</t>
+          <t>27402</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>16371</t>
+          <t>19133</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>33269</t>
+          <t>37490</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,14%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>26120</t>
+          <t>29450</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18207</t>
+          <t>20611</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>36011</t>
+          <t>40258</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>25564</t>
+          <t>28422</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18223</t>
+          <t>20971</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>34306</t>
+          <t>37481</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>51685</t>
+          <t>57871</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>40713</t>
+          <t>45315</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>63885</t>
+          <t>71337</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,89%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>161575</t>
+          <t>175014</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>141132</t>
+          <t>151683</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>182284</t>
+          <t>197874</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>36,22%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>40,31%</t>
+          <t>40,95%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>115526</t>
+          <t>127056</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>100506</t>
+          <t>111523</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>130274</t>
+          <t>142919</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>30,15%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>277101</t>
+          <t>302070</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>252440</t>
+          <t>274532</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>300331</t>
+          <t>331683</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>36,67%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>252117</t>
+          <t>265338</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>231694</t>
+          <t>243615</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>275433</t>
+          <t>288527</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>55,75%</t>
+          <t>54,91%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>51,24%</t>
+          <t>50,42%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>60,91%</t>
+          <t>59,71%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>228383</t>
+          <t>251907</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>212070</t>
+          <t>234230</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>243680</t>
+          <t>268430</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>59,96%</t>
+          <t>59,78%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>55,67%</t>
+          <t>55,59%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>63,97%</t>
+          <t>63,7%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>480500</t>
+          <t>517245</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>453352</t>
+          <t>488652</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>506415</t>
+          <t>546285</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>57,67%</t>
+          <t>57,18%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>54,42%</t>
+          <t>54,02%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>60,79%</t>
+          <t>60,39%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>380908</t>
+          <t>421377</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>380908</t>
+          <t>421377</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>380908</t>
+          <t>421377</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>833121</t>
+          <t>904589</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>833121</t>
+          <t>904589</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>833121</t>
+          <t>904589</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>262907</t>
+          <t>20218</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>23960</t>
+          <t>13805</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>504349</t>
+          <t>29959</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,47%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,17 +1898,17 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>6766</t>
+          <t>7589</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3687</t>
+          <t>4245</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>11234</t>
+          <t>13398</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>269673</t>
+          <t>27807</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>32142</t>
+          <t>20403</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>571503</t>
+          <t>39121</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>68,43%</t>
+          <t>5,94%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>32017</t>
+          <t>35023</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11018</t>
+          <t>24972</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>55318</t>
+          <t>48095</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>19330</t>
+          <t>20830</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>13485</t>
+          <t>14582</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>25980</t>
+          <t>28324</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>51348</t>
+          <t>55853</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>22623</t>
+          <t>44363</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>77393</t>
+          <t>70301</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>10,67%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>118285</t>
+          <t>135971</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>49747</t>
+          <t>116432</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>197786</t>
+          <t>156387</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>33,16%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>53631</t>
+          <t>60219</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>44796</t>
+          <t>49520</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>63678</t>
+          <t>71465</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>38,15%</t>
+          <t>38,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>171916</t>
+          <t>196191</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>77012</t>
+          <t>174542</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>247059</t>
+          <t>218234</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>33,11%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>255055</t>
+          <t>280400</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>98187</t>
+          <t>257879</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>413198</t>
+          <t>302182</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>59,46%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>54,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>61,83%</t>
+          <t>64,07%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>87184</t>
+          <t>98858</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>76747</t>
+          <t>87911</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>96973</t>
+          <t>109818</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>52,23%</t>
+          <t>52,73%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>45,98%</t>
+          <t>46,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>58,1%</t>
+          <t>58,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>342239</t>
+          <t>379258</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>162813</t>
+          <t>355945</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>496533</t>
+          <t>404918</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>40,98%</t>
+          <t>57,54%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>54,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>59,45%</t>
+          <t>61,43%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>40268</t>
+          <t>45175</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>30212</t>
+          <t>33975</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>52562</t>
+          <t>58766</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>23554</t>
+          <t>26460</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12140</t>
+          <t>19665</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>35273</t>
+          <t>35318</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>63822</t>
+          <t>71635</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>42679</t>
+          <t>58032</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>79207</t>
+          <t>88021</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,42%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>91749</t>
+          <t>102473</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>75707</t>
+          <t>84270</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>110873</t>
+          <t>123095</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>50088</t>
+          <t>57251</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>25744</t>
+          <t>45014</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>70847</t>
+          <t>70541</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>141836</t>
+          <t>159725</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>96976</t>
+          <t>136111</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>169177</t>
+          <t>182037</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>9,14%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>348384</t>
+          <t>377034</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>315544</t>
+          <t>345393</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>385291</t>
+          <t>410580</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>33,34%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>30,54%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>36,31%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>252107</t>
+          <t>285111</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>144176</t>
+          <t>264659</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>329296</t>
+          <t>311592</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>36,18%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>600491</t>
+          <t>662145</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>401845</t>
+          <t>626516</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>684226</t>
+          <t>710387</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>35,66%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>553551</t>
+          <t>606232</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>514921</t>
+          <t>569685</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>587462</t>
+          <t>641623</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>53,54%</t>
+          <t>53,61%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>50,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>56,82%</t>
+          <t>56,73%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>652345</t>
+          <t>492389</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>554960</t>
+          <t>463667</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>783818</t>
+          <t>515170</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>57,17%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>56,74%</t>
+          <t>53,84%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>80,14%</t>
+          <t>59,82%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1205895</t>
+          <t>1098622</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1100277</t>
+          <t>1048460</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1476834</t>
+          <t>1139615</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>59,93%</t>
+          <t>55,15%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>54,68%</t>
+          <t>52,63%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>73,4%</t>
+          <t>57,21%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1033951</t>
+          <t>1130915</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1033951</t>
+          <t>1130915</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1033951</t>
+          <t>1130915</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2012045</t>
+          <t>1992127</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2012045</t>
+          <t>1992127</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2012045</t>
+          <t>1992127</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>34541</t>
+          <t>48258</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>24596</t>
+          <t>36128</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>45228</t>
+          <t>64636</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>48730</t>
+          <t>59102</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>35729</t>
+          <t>48117</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>60836</t>
+          <t>71704</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
+          <t>7,13%</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
           <t>5,8%</t>
         </is>
       </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>4,25%</t>
-        </is>
-      </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>83271</t>
+          <t>107360</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>66351</t>
+          <t>90684</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>101333</t>
+          <t>128454</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>9,19%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>48978</t>
+          <t>54859</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>38741</t>
+          <t>42148</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>64021</t>
+          <t>68937</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>90585</t>
+          <t>104242</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>65888</t>
+          <t>89044</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>108383</t>
+          <t>121868</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>139562</t>
+          <t>159101</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>113947</t>
+          <t>140020</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>162574</t>
+          <t>182750</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>13,08%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>171305</t>
+          <t>205398</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>148484</t>
+          <t>181136</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>196585</t>
+          <t>232573</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>36,06%</t>
+          <t>36,16%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>31,89%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>40,95%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>264245</t>
+          <t>293031</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>201440</t>
+          <t>269829</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>303760</t>
+          <t>314254</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>35,34%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>37,9%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>435550</t>
+          <t>498429</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>361325</t>
+          <t>463553</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>478044</t>
+          <t>529546</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>35,67%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>33,18%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>37,9%</t>
         </is>
       </c>
     </row>
@@ -3340,32 +3340,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>220222</t>
+          <t>259449</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>197674</t>
+          <t>232638</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>243924</t>
+          <t>285950</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>46,36%</t>
+          <t>45,68%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>41,61%</t>
+          <t>40,96%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>51,35%</t>
+          <t>50,35%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>436239</t>
+          <t>372810</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>383101</t>
+          <t>350161</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>531864</t>
+          <t>398274</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>51,95%</t>
+          <t>44,96%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>45,62%</t>
+          <t>42,23%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>63,33%</t>
+          <t>48,03%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>656461</t>
+          <t>632259</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>598418</t>
+          <t>598548</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>783349</t>
+          <t>669501</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>49,93%</t>
+          <t>45,25%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>45,51%</t>
+          <t>42,84%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>59,58%</t>
+          <t>47,92%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>839799</t>
+          <t>829185</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>839799</t>
+          <t>829185</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>839799</t>
+          <t>829185</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1314845</t>
+          <t>1397149</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1314845</t>
+          <t>1397149</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1314845</t>
+          <t>1397149</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3555,7 +3555,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -3570,32 +3570,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2348</t>
+          <t>2256</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>493</t>
+          <t>733</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>7139</t>
+          <t>7401</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,32 +3605,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>36292</t>
+          <t>39497</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>27924</t>
+          <t>29065</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>49535</t>
+          <t>53379</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,17 +3640,17 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>38640</t>
+          <t>41753</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>30131</t>
+          <t>31941</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>53246</t>
+          <t>54225</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,02%</t>
         </is>
       </c>
     </row>
@@ -3683,32 +3683,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>6787</t>
+          <t>7960</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>3150</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>20483</t>
+          <t>20527</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,32 +3718,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>80625</t>
+          <t>91368</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>66958</t>
+          <t>77380</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>94967</t>
+          <t>108645</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,32 +3753,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>87412</t>
+          <t>99328</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>73136</t>
+          <t>82475</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>105937</t>
+          <t>118251</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,96%</t>
         </is>
       </c>
     </row>
@@ -3796,32 +3796,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>73495</t>
+          <t>75419</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>52067</t>
+          <t>53437</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>102816</t>
+          <t>97883</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>42,75%</t>
+          <t>41,26%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3831,32 +3831,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>291391</t>
+          <t>321547</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>267377</t>
+          <t>293231</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>319517</t>
+          <t>348739</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>38,19%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>34,83%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>41,42%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,32 +3866,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>364885</t>
+          <t>396966</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>332048</t>
+          <t>360625</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>404208</t>
+          <t>433778</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>36,79%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>33,42%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>40,44%</t>
+          <t>40,2%</t>
         </is>
       </c>
     </row>
@@ -3909,32 +3909,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>157877</t>
+          <t>151593</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>128858</t>
+          <t>128187</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>179772</t>
+          <t>176148</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>65,64%</t>
+          <t>63,9%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>53,58%</t>
+          <t>54,04%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>74,75%</t>
+          <t>74,25%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3944,32 +3944,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>350830</t>
+          <t>389500</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>325846</t>
+          <t>358533</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>377205</t>
+          <t>418940</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>46,26%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>42,92%</t>
+          <t>42,59%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>49,69%</t>
+          <t>49,76%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3979,32 +3979,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>508707</t>
+          <t>541092</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>468444</t>
+          <t>501304</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>544309</t>
+          <t>578354</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>50,14%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>46,86%</t>
+          <t>46,45%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>54,45%</t>
+          <t>53,59%</t>
         </is>
       </c>
     </row>
@@ -4022,17 +4022,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4057,17 +4057,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>759138</t>
+          <t>841912</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>759138</t>
+          <t>841912</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>759138</t>
+          <t>841912</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>999645</t>
+          <t>1079139</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>999645</t>
+          <t>1079139</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>999645</t>
+          <t>1079139</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4139,32 +4139,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>366058</t>
+          <t>143699</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>123777</t>
+          <t>122170</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>1182880</t>
+          <t>167235</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4174,32 +4174,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>136897</t>
+          <t>158662</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>111684</t>
+          <t>137294</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>158726</t>
+          <t>179312</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,32 +4209,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>502955</t>
+          <t>302361</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>258132</t>
+          <t>273149</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>1314002</t>
+          <t>333189</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>4,71%</t>
         </is>
       </c>
     </row>
@@ -4252,32 +4252,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>237735</t>
+          <t>267360</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>186223</t>
+          <t>238406</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>276516</t>
+          <t>299701</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4287,32 +4287,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>293681</t>
+          <t>335088</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>235939</t>
+          <t>306734</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>326710</t>
+          <t>367207</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,32 +4322,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>531416</t>
+          <t>602448</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>461734</t>
+          <t>563613</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>584809</t>
+          <t>650540</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>9,2%</t>
         </is>
       </c>
     </row>
@@ -4365,32 +4365,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>1010729</t>
+          <t>1117687</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>755489</t>
+          <t>1059212</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>1116313</t>
+          <t>1182351</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4400,32 +4400,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>1106558</t>
+          <t>1227277</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>885868</t>
+          <t>1175291</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>1202126</t>
+          <t>1276087</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>32,38%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>35,16%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,32 +4435,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>2117287</t>
+          <t>2344964</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1859917</t>
+          <t>2269500</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>2270272</t>
+          <t>2429287</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>34,36%</t>
         </is>
       </c>
     </row>
@@ -4478,32 +4478,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>1759645</t>
+          <t>1911648</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1267274</t>
+          <t>1848037</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1917814</t>
+          <t>1976256</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>52,15%</t>
+          <t>55,56%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>37,56%</t>
+          <t>53,72%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>56,84%</t>
+          <t>57,44%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4513,32 +4513,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>2035180</t>
+          <t>1908566</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1914922</t>
+          <t>1857416</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>2347612</t>
+          <t>1962455</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>56,97%</t>
+          <t>52,58%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>53,6%</t>
+          <t>51,17%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>65,72%</t>
+          <t>54,07%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4548,32 +4548,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>3794825</t>
+          <t>3820214</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>3375226</t>
+          <t>3737926</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>4061754</t>
+          <t>3902849</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>54,63%</t>
+          <t>54,03%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>48,59%</t>
+          <t>52,87%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>58,47%</t>
+          <t>55,2%</t>
         </is>
       </c>
     </row>
@@ -4591,17 +4591,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>3374167</t>
+          <t>3440394</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>3374167</t>
+          <t>3440394</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>3374167</t>
+          <t>3440394</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4626,17 +4626,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>3572316</t>
+          <t>3629593</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>3572316</t>
+          <t>3629593</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3572316</t>
+          <t>3629593</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>6946483</t>
+          <t>7069987</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>6946483</t>
+          <t>7069987</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>6946483</t>
+          <t>7069987</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
